--- a/GPIpuget/project/Pre Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Pre Hopper Run Checks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -39,10 +39,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
 </sst>
 </file>
@@ -433,7 +430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -451,11 +448,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Pre Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Pre Hopper Run Checks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -39,7 +39,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -448,6 +451,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Pre Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Pre Hopper Run Checks.xlsx
@@ -24,10 +24,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>

--- a/GPIpuget/project/Pre Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Pre Hopper Run Checks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -24,10 +24,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -39,10 +39,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
 </sst>
 </file>
@@ -433,7 +430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -451,11 +448,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Pre Hopper Run Checks.xlsx
+++ b/GPIpuget/project/Pre Hopper Run Checks.xlsx
@@ -24,10 +24,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
